--- a/Planilhas/SALAS.xlsx
+++ b/Planilhas/SALAS.xlsx
@@ -1,41 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\013190873\Downloads\Pessoal\VS\BB_Py_Automation\Planilhas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sereducacionalbr-my.sharepoint.com/personal/dhiego_moura_sereducacional_com/Documents/Documentos/BB_Py_Automation-dev/BB_Py_Automation/Planilhas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFACEBAE-C719-433E-A9CB-1A00C74F8600}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="11_A831CAF7196FC6FEBDF7265BE96BB01D44075CD0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D60E1653-6758-44EB-8E9A-40A82C818FF6}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1350" yWindow="1560" windowWidth="14730" windowHeight="11340" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="salas" sheetId="1" r:id="rId1"/>
     <sheet name="salaCopia" sheetId="2" r:id="rId2"/>
-    <sheet name="atividades" sheetId="3" r:id="rId3"/>
+    <sheet name="expurgo" sheetId="4" r:id="rId3"/>
+    <sheet name="atividades" sheetId="3" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="98">
   <si>
     <t>ID</t>
   </si>
@@ -326,19 +314,28 @@
   </si>
   <si>
     <t>Service Design</t>
+  </si>
+  <si>
+    <t>USER</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -351,11 +348,32 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFC6C6C6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFC6C6C6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFC6C6C6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFC6C6C6"/>
+      </bottom>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -365,24 +383,41 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2"/>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+  <cellXfs count="10">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -395,13 +430,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabela1" displayName="Tabela1" ref="A1:B79" totalsRowShown="0">
-  <autoFilter ref="A1:B79" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabela1" displayName="Tabela1" ref="A1:B79" totalsRowShown="0">
+  <autoFilter ref="A1:B79" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="CURSO"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="GRANDE ÁREA"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="CURSO"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="GRANDE ÁREA"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -440,20 +475,20 @@
         <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -483,12 +518,12 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -527,181 +562,325 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:tint val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:tint val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="9500"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:tint val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+  </sheetPr>
+  <dimension ref="A1:B114"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.6640625" customWidth="1"/>
+    <col min="1" max="1" width="19.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" style="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="4"/>
+    <row r="2" spans="1:2" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="18" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="19" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="20" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" spans="2:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" spans="2:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" spans="2:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B99" s="1"/>
+    </row>
+    <row r="100" spans="2:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" spans="2:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" spans="2:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" spans="2:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" spans="2:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" spans="2:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" spans="2:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" spans="2:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" spans="2:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" spans="2:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" spans="2:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" spans="2:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" spans="2:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" spans="2:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" spans="2:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B114" s="1"/>
     </row>
   </sheetData>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967294" verticalDpi="4294967294"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+  </sheetPr>
   <dimension ref="A1:C1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23" style="1" customWidth="1"/>
-    <col min="2" max="2" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B1" t="s">
@@ -713,20 +892,230 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967294" verticalDpi="4294967294"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E8C6456-2450-485E-AC53-AFD9A36CC2D4}">
+  <dimension ref="A1:C47"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="21.42578125" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="8"/>
+      <c r="C2" s="3"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="7"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="7"/>
+      <c r="C4" s="5"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="7"/>
+      <c r="C5" s="5"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="7"/>
+      <c r="C6" s="5"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="7"/>
+      <c r="C7" s="5"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="7"/>
+      <c r="C8" s="5"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="7"/>
+      <c r="C9" s="5"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="7"/>
+      <c r="C10" s="5"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="7"/>
+      <c r="C11" s="5"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="7"/>
+      <c r="C12" s="5"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="7"/>
+      <c r="C13" s="5"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="7"/>
+      <c r="C14" s="5"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="7"/>
+      <c r="C15" s="5"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="7"/>
+      <c r="C16" s="5"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="7"/>
+      <c r="C17" s="5"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="7"/>
+      <c r="C18" s="5"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="7"/>
+      <c r="C19" s="5"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="7"/>
+      <c r="C20" s="5"/>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="7"/>
+      <c r="C21" s="5"/>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="7"/>
+      <c r="C22" s="5"/>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="7"/>
+      <c r="C23" s="5"/>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="7"/>
+      <c r="C24" s="5"/>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="7"/>
+      <c r="C25" s="5"/>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="7"/>
+      <c r="C26" s="5"/>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="7"/>
+      <c r="C27" s="5"/>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="7"/>
+      <c r="C28" s="5"/>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="7"/>
+      <c r="C29" s="5"/>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="7"/>
+      <c r="C30" s="5"/>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="7"/>
+      <c r="C31" s="5"/>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="7"/>
+      <c r="C32" s="5"/>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="7"/>
+      <c r="C33" s="5"/>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="7"/>
+      <c r="C34" s="5"/>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="7"/>
+      <c r="C35" s="6"/>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="7"/>
+      <c r="C36" s="5"/>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="7"/>
+      <c r="C37" s="5"/>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="9"/>
+      <c r="C38" s="5"/>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="9"/>
+      <c r="C39" s="5"/>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="9"/>
+      <c r="C40" s="5"/>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="9"/>
+      <c r="C41" s="5"/>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="9"/>
+      <c r="C42" s="5"/>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="9"/>
+      <c r="C43" s="5"/>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="9"/>
+      <c r="C44" s="5"/>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="9"/>
+      <c r="C45" s="5"/>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="9"/>
+      <c r="C46" s="5"/>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="9"/>
+      <c r="C47" s="5"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+  </sheetPr>
   <dimension ref="A1:B79"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="73" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -734,63 +1123,63 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+    <row r="5" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+    <row r="6" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+    <row r="7" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
+    <row r="8" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -798,7 +1187,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -806,7 +1195,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -814,7 +1203,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -822,7 +1211,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -830,7 +1219,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>19</v>
       </c>
@@ -838,7 +1227,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>21</v>
       </c>
@@ -846,7 +1235,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>22</v>
       </c>
@@ -854,7 +1243,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>23</v>
       </c>
@@ -862,7 +1251,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>24</v>
       </c>
@@ -870,7 +1259,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>25</v>
       </c>
@@ -878,7 +1267,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>26</v>
       </c>
@@ -886,7 +1275,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>27</v>
       </c>
@@ -894,7 +1283,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>28</v>
       </c>
@@ -902,7 +1291,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>30</v>
       </c>
@@ -910,7 +1299,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>31</v>
       </c>
@@ -918,7 +1307,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>32</v>
       </c>
@@ -926,7 +1315,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>33</v>
       </c>
@@ -934,7 +1323,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>34</v>
       </c>
@@ -942,7 +1331,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>35</v>
       </c>
@@ -950,7 +1339,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>36</v>
       </c>
@@ -958,7 +1347,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>37</v>
       </c>
@@ -966,7 +1355,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>38</v>
       </c>
@@ -974,7 +1363,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>40</v>
       </c>
@@ -982,7 +1371,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>42</v>
       </c>
@@ -990,7 +1379,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>43</v>
       </c>
@@ -998,7 +1387,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>44</v>
       </c>
@@ -1006,7 +1395,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>45</v>
       </c>
@@ -1014,7 +1403,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>46</v>
       </c>
@@ -1022,7 +1411,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>48</v>
       </c>
@@ -1030,7 +1419,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>49</v>
       </c>
@@ -1038,7 +1427,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>50</v>
       </c>
@@ -1046,7 +1435,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>51</v>
       </c>
@@ -1054,7 +1443,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>53</v>
       </c>
@@ -1062,7 +1451,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>54</v>
       </c>
@@ -1070,7 +1459,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>55</v>
       </c>
@@ -1078,7 +1467,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>56</v>
       </c>
@@ -1086,7 +1475,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>57</v>
       </c>
@@ -1094,7 +1483,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>58</v>
       </c>
@@ -1102,7 +1491,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>59</v>
       </c>
@@ -1110,7 +1499,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>60</v>
       </c>
@@ -1118,7 +1507,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>61</v>
       </c>
@@ -1126,7 +1515,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>62</v>
       </c>
@@ -1134,7 +1523,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>63</v>
       </c>
@@ -1142,7 +1531,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>64</v>
       </c>
@@ -1150,7 +1539,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>66</v>
       </c>
@@ -1158,7 +1547,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>67</v>
       </c>
@@ -1166,7 +1555,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>68</v>
       </c>
@@ -1174,7 +1563,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>69</v>
       </c>
@@ -1182,7 +1571,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>71</v>
       </c>
@@ -1190,7 +1579,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>72</v>
       </c>
@@ -1198,7 +1587,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>73</v>
       </c>
@@ -1206,7 +1595,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>75</v>
       </c>
@@ -1214,7 +1603,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>76</v>
       </c>
@@ -1222,7 +1611,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>78</v>
       </c>
@@ -1230,7 +1619,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>79</v>
       </c>
@@ -1238,7 +1627,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>80</v>
       </c>
@@ -1246,7 +1635,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>81</v>
       </c>
@@ -1254,7 +1643,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>83</v>
       </c>
@@ -1262,7 +1651,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>84</v>
       </c>
@@ -1270,7 +1659,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>86</v>
       </c>
@@ -1278,7 +1667,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>87</v>
       </c>
@@ -1286,7 +1675,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>88</v>
       </c>
@@ -1294,7 +1683,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>89</v>
       </c>
@@ -1302,7 +1691,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>90</v>
       </c>
@@ -1310,7 +1699,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>91</v>
       </c>
@@ -1318,7 +1707,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>92</v>
       </c>
@@ -1326,7 +1715,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>93</v>
       </c>
@@ -1334,7 +1723,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>94</v>
       </c>
@@ -1342,7 +1731,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>95</v>
       </c>
@@ -1350,7 +1739,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>96</v>
       </c>
@@ -1359,8 +1748,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967294" verticalDpi="4294967294"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>

--- a/Planilhas/SALAS.xlsx
+++ b/Planilhas/SALAS.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sereducacionalbr-my.sharepoint.com/personal/dhiego_moura_sereducacional_com/Documents/Documentos/BB_Py_Automation-dev/BB_Py_Automation/Planilhas/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\013190873\Documents\VS\BB_Py_Automation\planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="11_A831CAF7196FC6FEBDF7265BE96BB01D44075CD0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D60E1653-6758-44EB-8E9A-40A82C818FF6}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE6121A9-B5FB-4A4B-9717-88F78B5D83CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1350" yWindow="1560" windowWidth="14730" windowHeight="11340" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="salas" sheetId="1" r:id="rId1"/>
@@ -385,7 +385,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -397,19 +397,10 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
@@ -728,137 +719,20 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:B114"/>
+  <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.5703125" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.5703125" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="18" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="19" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="20" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="22" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="26" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="27" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="33" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="34" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="35" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="36" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="37" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="38" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="39" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="40" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="41" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="42" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="43" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="44" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="46" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="47" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="48" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="49" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="50" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="51" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="52" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="53" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="54" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="55" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="56" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="57" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="58" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="65" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="66" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="67" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="69" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="70" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="71" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="72" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="73" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="76" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="77" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="80" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="82" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="83" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="91" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="92" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="93" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="94" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="97" spans="2:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="98" spans="2:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="99" spans="2:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B99" s="1"/>
-    </row>
-    <row r="100" spans="2:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="101" spans="2:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="102" spans="2:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="103" spans="2:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="104" spans="2:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="105" spans="2:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="106" spans="2:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="107" spans="2:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="108" spans="2:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="109" spans="2:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="110" spans="2:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="111" spans="2:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="112" spans="2:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="113" spans="2:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="114" spans="2:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B114" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -897,7 +771,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E8C6456-2450-485E-AC53-AFD9A36CC2D4}">
-  <dimension ref="A1:C47"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.42578125" customWidth="1"/>
@@ -905,7 +779,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -914,189 +788,6 @@
       <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="8"/>
-      <c r="C2" s="3"/>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="7"/>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="7"/>
-      <c r="C4" s="5"/>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="7"/>
-      <c r="C5" s="5"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="7"/>
-      <c r="C6" s="5"/>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="7"/>
-      <c r="C7" s="5"/>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="7"/>
-      <c r="C8" s="5"/>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="7"/>
-      <c r="C9" s="5"/>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="7"/>
-      <c r="C10" s="5"/>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="7"/>
-      <c r="C11" s="5"/>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="7"/>
-      <c r="C12" s="5"/>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="7"/>
-      <c r="C13" s="5"/>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="7"/>
-      <c r="C14" s="5"/>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="7"/>
-      <c r="C15" s="5"/>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="7"/>
-      <c r="C16" s="5"/>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="7"/>
-      <c r="C17" s="5"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="7"/>
-      <c r="C18" s="5"/>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="7"/>
-      <c r="C19" s="5"/>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="7"/>
-      <c r="C20" s="5"/>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="7"/>
-      <c r="C21" s="5"/>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="7"/>
-      <c r="C22" s="5"/>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="7"/>
-      <c r="C23" s="5"/>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="7"/>
-      <c r="C24" s="5"/>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="7"/>
-      <c r="C25" s="5"/>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="7"/>
-      <c r="C26" s="5"/>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="7"/>
-      <c r="C27" s="5"/>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="7"/>
-      <c r="C28" s="5"/>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="7"/>
-      <c r="C29" s="5"/>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="7"/>
-      <c r="C30" s="5"/>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="7"/>
-      <c r="C31" s="5"/>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="7"/>
-      <c r="C32" s="5"/>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="7"/>
-      <c r="C33" s="5"/>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="7"/>
-      <c r="C34" s="5"/>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="7"/>
-      <c r="C35" s="6"/>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="7"/>
-      <c r="C36" s="5"/>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="7"/>
-      <c r="C37" s="5"/>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="9"/>
-      <c r="C38" s="5"/>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="9"/>
-      <c r="C39" s="5"/>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="9"/>
-      <c r="C40" s="5"/>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="9"/>
-      <c r="C41" s="5"/>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="9"/>
-      <c r="C42" s="5"/>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="9"/>
-      <c r="C43" s="5"/>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="9"/>
-      <c r="C44" s="5"/>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="9"/>
-      <c r="C45" s="5"/>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="9"/>
-      <c r="C46" s="5"/>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="9"/>
-      <c r="C47" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
